--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XX/LTAIPT_A63F20.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XX/LTAIPT_A63F20.xlsx
@@ -181,34 +181,34 @@
     <t>Nombre del trámite</t>
   </si>
   <si>
-    <t>Descripción de trámite</t>
-  </si>
-  <si>
-    <t>Tipo de usuario y/o población objetivo</t>
+    <t>Descripción de trámite (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Tipo de población usuaria y/o población objetivo (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Modalidad del trámite</t>
   </si>
   <si>
-    <t>Hipervínculo a los requisitos para llevar a cabo el trámite</t>
-  </si>
-  <si>
-    <t>Documentos requeridos, en su caso</t>
+    <t>Hipervínculo a los requisitos para llevar a cabo el trámite (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Documentos requeridos, en su caso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Hipervínculo al/los formatos respectivos</t>
   </si>
   <si>
-    <t>Última fecha de publicación en el medio de difusión</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Última fecha de publicación en el medio de difusión</t>
   </si>
   <si>
     <t>Tiempo de respuesta por parte del sujeto Obligado</t>
   </si>
   <si>
-    <t>Plazo con el que cuenta el sujeto obligado para prevenir al solicitante</t>
-  </si>
-  <si>
-    <t>Plazo con el que cuenta el solicitante para cumplir con la prevención</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Plazo con el que cuenta el sujeto obligado para prevenir al solicitante</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Plazo con el que cuenta el solicitante para cumplir con la prevención</t>
   </si>
   <si>
     <t>Vigencia de los resultados del trámite</t>
@@ -218,7 +218,7 @@
 Tabla_436126</t>
   </si>
   <si>
-    <t>Monto de los derechos o aprovechamientos aplicables, en su caso</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Monto de los derechos o aprovechamientos aplicables, en su caso</t>
   </si>
   <si>
     <t>Sustento legal para su cobro</t>
@@ -231,10 +231,10 @@
     <t>Fundamento jurídico-administrativo de la existencia del trámite</t>
   </si>
   <si>
-    <t>Derechos del usuario</t>
-  </si>
-  <si>
-    <t>Información adicional del trámite, en su caso</t>
+    <t>Derechos de la persona usuaria ante la negativa o la falta de respuesta (especificar si aplica la afirmativa o negativa ficta) (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Información adicional del trámite, en su caso (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Medio que permita el envío de consultas y documentos 
@@ -260,16 +260,73 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>5D17E24B97F3CD069488054F95B7E009</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>ACCD629F01BAA4B26C18B5EB418D5672</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Revalidación de Estudios por Semestre</t>
+  </si>
+  <si>
+    <t>Procedimiento administrativo que se inicia a petición del aspirante a alumno que cuenta con estudios parciales de Educación Media Superior realizados en instituciones del Sistema Educativo Nacional, y/o con certificado de competencia laboral con el fin de que se equiparen sus estudios a los del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>http://www.tlaxcalaenlinea.gob.mx</t>
+  </si>
+  <si>
+    <t>No adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, Certificado Parcial de la Institución de origen (original y dos copias), Certificado de Secundaria (original y dos copias), Acta de Nacimiento (original y dos copias), Clave Única de Registro de Población (original y dos copias) , Número de Seguridad Social Instituto Mexicano del Seguro Social (original y dos copias), Formato de baja de Seguro Instituto Mexicano del Seguo Social de la escuela anterior (original y dos copias), Comprobante de domicilio (original y dos copias), Copia de recibo de pago por semestres revalidados</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Tres días hábiles</t>
+  </si>
+  <si>
+    <t>Ver nota</t>
+  </si>
+  <si>
+    <t>Por el semestre</t>
+  </si>
+  <si>
+    <t>6251336</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III el Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción VII. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50</t>
+  </si>
+  <si>
+    <t>Queja ante la Contraloría del Ejecutivo del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Revalidación de Estudios por Semestre.  El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Revalidación de Estudios por Semestre). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>0173D9DD4F92D6A4E3EFF3824AAF1F81</t>
   </si>
   <si>
     <t>Duplicado de Certificado de Terminación de Estudios</t>
@@ -281,12 +338,6 @@
     <t>Ex-alumnos del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>http://www.tlaxcalaenlinea.gob.mx</t>
-  </si>
-  <si>
     <t>Solicitud de Trámite (proporcionada en el plantel donde cursó), Pago de Derechos, Productos y Aprovechamientos, seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje</t>
   </si>
   <si>
@@ -299,40 +350,19 @@
     <t>Quince días hábiles</t>
   </si>
   <si>
-    <t>Ver nota</t>
-  </si>
-  <si>
-    <t>Por el semestre</t>
-  </si>
-  <si>
-    <t>4826109</t>
+    <t>6251335</t>
   </si>
   <si>
     <t>187</t>
   </si>
   <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III el Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
-  </si>
-  <si>
     <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción III. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción IV</t>
   </si>
   <si>
-    <t>Queja ante la Contraloría del Ejecutivo del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Duplicado de Certificado de Terminación de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>44155382C6549CAAAC1F2F59FC9BC094</t>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Duplicado de Certificado de Terminación de Estudios). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>C39DD526464EE824755638EFEB3D0FD3</t>
   </si>
   <si>
     <t>Duplicado de Carta de Buena Conducta</t>
@@ -353,7 +383,7 @@
     <t>Un día  hábil</t>
   </si>
   <si>
-    <t>4826108</t>
+    <t>6251334</t>
   </si>
   <si>
     <t>50</t>
@@ -362,10 +392,10 @@
     <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción IV</t>
   </si>
   <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Duplicado de Carta de Buena Conducta). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>BEC401120FAEB9FF2C50DCE221EF5EA8</t>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Duplicado de Carta de Buena Conducta). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>2F98F7ED8E825DC77D61967CD3287827</t>
   </si>
   <si>
     <t>Constancia de Estudios</t>
@@ -380,43 +410,13 @@
     <t>Solicitud de Trámite (proporcionada en el plantel donde cursa), Pago de Derechos, Productos y Aprovechamientos</t>
   </si>
   <si>
-    <t>4826107</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Constancia de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>0D3DDBBC367407C9BA925D19CDA0D592</t>
-  </si>
-  <si>
-    <t>Revalidación de Estudios por Semestre</t>
-  </si>
-  <si>
-    <t>Procedimiento administrativo que se inicia a petición del aspirante a alumno que cuenta con estudios parciales de Educación Media Superior realizados en instituciones del Sistema Educativo Nacional, y/o con certificado de competencia laboral con el fin de que se equiparen sus estudios a los del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>No adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, Certificado Parcial de la Institución de origen (original y dos copias), Certificado de Secundaria (original y dos copias), Acta de Nacimiento (original y dos copias), Clave Única de Registro de Población (original y dos copias) , Número de Seguridad Social Instituto Mexicano del Seguro Social (original y dos copias), Formato de baja de Seguro Instituto Mexicano del Seguo Social de la escuela anterior (original y dos copias), Comprobante de domicilio (original y dos copias), Copia de recibo de pago por semestres revalidados</t>
-  </si>
-  <si>
-    <t>Tres días hábiles</t>
-  </si>
-  <si>
-    <t>4826110</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción VII. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Revalidación de Estudios por Semestre.  El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Revalidación de Estudios por Semestre). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>221248E1E6974CAC7C9FA0C18BDE608A</t>
+    <t>6251333</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Constancia de Estudios). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>1BE9EBA63890EF97BB3E137F275A8297</t>
   </si>
   <si>
     <t>Constancia de Calificaciones</t>
@@ -428,16 +428,16 @@
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/CONSTANCIA%20DE%20CALIFICACIONES.pdf</t>
   </si>
   <si>
-    <t>4826106</t>
+    <t>6251332</t>
   </si>
   <si>
     <t>60</t>
   </si>
   <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Constancia de Calificaciones). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>0FF321B53F5D36BEA49B64EC1688F6D4</t>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Constancia de Calificaciones). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>BB251C9EFAC9F191E2BA7C4FBACB1DA7</t>
   </si>
   <si>
     <t>Certificado Parcial de Estudios</t>
@@ -449,16 +449,16 @@
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/CERTIFICADO%20PARCIAL%20DE%20ESTUDIOS.pdf</t>
   </si>
   <si>
-    <t>4826105</t>
+    <t>6251331</t>
   </si>
   <si>
     <t>135</t>
   </si>
   <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Certificado Parcial de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>C15736DE8DD26ACE260A066D9F0ED0AC</t>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Certificado Parcial de Estudios). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>54883E49949E144870C87291C46CFB67</t>
   </si>
   <si>
     <t>Certificado Completo de Estudios</t>
@@ -470,10 +470,10 @@
     <t>Solicitud de Trámite (proporcionada en el plantel donde cursa), Pago de Derechos, Productos y Aprovechamientos (incluye pago de paquete de fin de cursos),  seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, dos fotografías tamaño diploma</t>
   </si>
   <si>
-    <t>4826104</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Certificado Completo de Estudios. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Certificado Completo de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+    <t>6251330</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Certificado Completo de Estudios. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Certificado Completo de Estudios). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
   </si>
   <si>
     <t>9</t>
@@ -590,15 +590,54 @@
     <t>Horario de atención(días y horas)</t>
   </si>
   <si>
-    <t>FB2115CFBB440146AA054253D1D10D6F</t>
+    <t>8E70D2C2253187343E9BF2EDD3227EF7</t>
+  </si>
+  <si>
+    <t>Dirección Administrativa</t>
+  </si>
+  <si>
+    <t>Calle</t>
+  </si>
+  <si>
+    <t>Emiliano Zapata</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Panotla</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2464628521</t>
+  </si>
+  <si>
+    <t>Dir.Administrativa@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Lunes a viernes de 8:30 a 17:30 horas</t>
+  </si>
+  <si>
+    <t>8E70D2C225318734BAB7700CC72A47BE</t>
   </si>
   <si>
     <t>Control Escolar de cada uno de los 24 planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>Calle</t>
-  </si>
-  <si>
     <t>Miguel N. Lira</t>
   </si>
   <si>
@@ -608,67 +647,28 @@
     <t>Colonia</t>
   </si>
   <si>
-    <t>Tlaxcala</t>
-  </si>
-  <si>
     <t>33</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
     <t>2464623323</t>
   </si>
   <si>
     <t>Servicios.Edu@cobatlaxcala.edu.mx</t>
   </si>
   <si>
-    <t>Lunes a viernes de 8:30 a 17:30 horas</t>
-  </si>
-  <si>
-    <t>FB2115CFBB44014609103D05A0949F13</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5F0857079D1D4A58C</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146A16DDE16C23C1F2F</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
-  </si>
-  <si>
-    <t>Emiliano Zapata</t>
-  </si>
-  <si>
-    <t>S/N</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Panotla</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2464628521</t>
-  </si>
-  <si>
-    <t>Dir.Administrativa@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF56A67A33217DF80AE</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271DE0D5BE9ADE31727</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D127153249C5697510FAD</t>
+    <t>2B7B91D1D16869E8001290DF6016565D</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E8AE2D2A4F6518FE97</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E82CCD89ADD6D2F26A</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF02405C3280F1B9FB2F4</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF024C700289253703180</t>
   </si>
   <si>
     <t>Carretera</t>
@@ -953,28 +953,28 @@
     <t>Lugares donde se efectúa el pago</t>
   </si>
   <si>
-    <t>FB2115CFBB44014659556362896F385C</t>
+    <t>8E70D2C2253187344697E3E517978EC0</t>
+  </si>
+  <si>
+    <t>8E70D2C2253187342B6FC0CA5E3D31A7</t>
   </si>
   <si>
     <t>Instituciones bancarias (Bancomer, Santander, HSBC, Scotiabank, Banorte, Citibanamex) Pago de Servicios Banca Electrónica Clientes Bancomer / HSBC, Transferencia electrónica de otros bancos (Bancomer, HSBC), Tiendas ANTAD (Chedraui, Farmacias del Ahorro, Soriana, Multired Global, Extra, Transfer, Bodega Aurrera, Walmart, SAM´S Club, Superama, Elektra, Banco Azteca) Receptoras de pago con cobro de comisión (Telecomm, HSBC RAP 2900, Oxxo)</t>
   </si>
   <si>
-    <t>FB2115CFBB440146662F09D622F87A27</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5D71634BF23CE9C03</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146CB4D92342CB2037C</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF58267AE3A5603544D</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271324E4A5495145B89</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D127172234A927D7B31B0</t>
+    <t>2B7B91D1D16869E8602A11B52270DFB3</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E8AE3CCD4EDD2233C6</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E8E24B006707E51597</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF024AA42EF2774FDE941</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF024244B1AAB3714B788</t>
   </si>
   <si>
     <t>76320</t>
@@ -1046,25 +1046,25 @@
     <t>Código postal</t>
   </si>
   <si>
-    <t>FB2115CFBB440146337462A6C6073EB8</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146CAB0FD84B7C4B6DC</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF51300D1EC26EBE6EC</t>
-  </si>
-  <si>
-    <t>82BE20F1A5758727D49FBDFA09FFA573</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5CB4F5691590F89EA</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF519F29A68A3FA9A1F</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271E3731360E0A38DE8</t>
+    <t>8E70D2C22531873473A1BBE55678EF29</t>
+  </si>
+  <si>
+    <t>8E70D2C2253187348E94C50AE4B7C6F9</t>
+  </si>
+  <si>
+    <t>8E70D2C2253187345B791B03CF1BBC5D</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E84C33ED37D5CA991E</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E84B15F79651521065</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF024FDEE777AFD01BA6B</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF024D252B09DF0BCD433</t>
   </si>
   <si>
     <t>56400</t>
@@ -1142,7 +1142,7 @@
     <t>Entidad federativa</t>
   </si>
   <si>
-    <t>FB2115CFBB44014674EA69810E255BE3</t>
+    <t>8E70D2C225318734AE5236946D7AEF83</t>
   </si>
   <si>
     <t>01 246 465 0900 Ext. 2113,2114,2139</t>
@@ -1163,22 +1163,22 @@
     <t>90600</t>
   </si>
   <si>
-    <t>FB2115CFBB440146CC43F01B0074418B</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF53F3838359232C641</t>
-  </si>
-  <si>
-    <t>82BE20F1A57587273181E15556F81341</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5F7B7CEDF8F2C84A9</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF582CB1B3CA2FD893D</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271FAC1E6E3B2D7C7BB</t>
+    <t>8E70D2C225318734B6BDC01224991543</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E8B25D83513A57967E</t>
+  </si>
+  <si>
+    <t>2B7B91D1D16869E8822FE37749A9DB7C</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF0248824524ECE72EBA4</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF0241D00242CCCF61A64</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF0240FF30A9A936D4E37</t>
   </si>
 </sst>
 </file>
@@ -1577,29 +1577,29 @@
   <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="255" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="119.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="83.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="255" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="180" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="88.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="103.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="102.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="53.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="100.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="132" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="245" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="138" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="116.28515625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="47.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="78.7109375" bestFit="1" customWidth="1"/>
@@ -1982,66 +1982,66 @@
         <v>82</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="N8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="W8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="AA8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD8" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>73</v>
@@ -2053,13 +2053,13 @@
         <v>75</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>79</v>
@@ -2068,72 +2068,72 @@
         <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="3" t="s">
+      <c r="R9" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="S9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="V9" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>80</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>73</v>
@@ -2145,13 +2145,13 @@
         <v>75</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>79</v>
@@ -2160,72 +2160,72 @@
         <v>80</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="Q10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>80</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>73</v>
@@ -2237,13 +2237,13 @@
         <v>75</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>79</v>
@@ -2252,64 +2252,64 @@
         <v>80</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="Q11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="U11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="Y11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>80</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AC11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AD11" s="3" t="s">
         <v>123</v>
@@ -2335,7 +2335,7 @@
         <v>126</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>79</v>
@@ -2344,25 +2344,25 @@
         <v>80</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>127</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="N12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>128</v>
@@ -2371,19 +2371,19 @@
         <v>129</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>128</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>128</v>
@@ -2395,13 +2395,13 @@
         <v>80</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>130</v>
@@ -2427,7 +2427,7 @@
         <v>126</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>79</v>
@@ -2442,19 +2442,19 @@
         <v>134</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="N13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>135</v>
@@ -2463,19 +2463,19 @@
         <v>136</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>135</v>
       </c>
       <c r="U13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="V13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="V13" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="W13" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>135</v>
@@ -2487,13 +2487,13 @@
         <v>80</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AC13" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AD13" s="3" t="s">
         <v>137</v>
@@ -2519,7 +2519,7 @@
         <v>140</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>79</v>
@@ -2531,43 +2531,43 @@
         <v>141</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>142</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>142</v>
       </c>
       <c r="U14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="W14" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>142</v>
@@ -2579,13 +2579,13 @@
         <v>80</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>143</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -2781,7 +2781,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="4" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>366</v>
@@ -2974,10 +2974,10 @@
         <v>369</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>255</v>
@@ -3001,18 +3001,18 @@
         <v>190</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>373</v>
@@ -3030,10 +3030,10 @@
         <v>369</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>255</v>
@@ -3057,18 +3057,18 @@
         <v>190</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>374</v>
@@ -3086,10 +3086,10 @@
         <v>369</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>255</v>
@@ -3113,18 +3113,18 @@
         <v>190</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>375</v>
@@ -3142,10 +3142,10 @@
         <v>369</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>255</v>
@@ -3169,13 +3169,13 @@
         <v>190</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3198,10 +3198,10 @@
         <v>369</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>255</v>
@@ -3225,13 +3225,13 @@
         <v>190</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3254,10 +3254,10 @@
         <v>369</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>255</v>
@@ -3281,13 +3281,13 @@
         <v>190</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3310,10 +3310,10 @@
         <v>369</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>255</v>
@@ -3337,13 +3337,13 @@
         <v>190</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>372</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -3539,7 +3539,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -3814,7 +3814,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="82.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>182</v>
@@ -4106,7 +4106,7 @@
         <v>186</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>187</v>
@@ -4130,208 +4130,208 @@
         <v>190</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>190</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>190</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="K7" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>190</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -4342,58 +4342,58 @@
         <v>206</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>190</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -4404,58 +4404,58 @@
         <v>207</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>190</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,58 +4466,58 @@
         <v>208</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>190</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -4713,7 +4713,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -5092,46 +5092,46 @@
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>303</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>304</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>306</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>307</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5142,7 +5142,7 @@
         <v>308</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
         <v>309</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5164,7 +5164,7 @@
         <v>310</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -5178,7 +5178,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -5342,214 +5342,214 @@
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>334</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>335</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>336</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>337</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5560,49 +5560,49 @@
         <v>338</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5613,49 +5613,49 @@
         <v>339</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5666,49 +5666,49 @@
         <v>340</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5894,7 +5894,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -5904,7 +5904,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
